--- a/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:41</t>
+          <t>2026-08-31 17:11:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>999</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.39%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:41</t>
+          <t>2026-08-31 17:11:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:41</t>
+          <t>2026-08-31 17:11:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:41</t>
+          <t>2026-08-31 17:11:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:41</t>
+          <t>2026-08-31 17:11:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:42</t>
+          <t>2026-08-31 17:11:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:42</t>
+          <t>2026-08-31 17:11:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:42</t>
+          <t>2026-08-31 17:11:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:42</t>
+          <t>2026-08-31 17:11:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,17 +1013,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:42</t>
+          <t>2026-08-31 17:11:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:44</t>
+          <t>2026-08-31 17:11:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:44</t>
+          <t>2026-08-31 17:11:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:44</t>
+          <t>2026-08-31 17:11:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>584</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:44</t>
+          <t>2026-08-31 17:11:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:44</t>
+          <t>2026-08-31 17:11:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:45</t>
+          <t>2026-08-31 17:11:12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+9.09%270</t>
+          <t>-4.81%257</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+9.09%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">

--- a/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:07</t>
+          <t>2026-08-31 19:31:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:07</t>
+          <t>2026-08-31 19:31:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:07</t>
+          <t>2026-08-31 19:31:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:07</t>
+          <t>2026-08-31 19:31:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:07</t>
+          <t>2026-08-31 19:31:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:09</t>
+          <t>2026-08-31 19:31:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:09</t>
+          <t>2026-08-31 19:31:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:09</t>
+          <t>2026-08-31 19:31:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:09</t>
+          <t>2026-08-31 19:31:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:09</t>
+          <t>2026-08-31 19:31:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:10</t>
+          <t>2026-08-31 19:31:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:10</t>
+          <t>2026-08-31 19:31:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:10</t>
+          <t>2026-08-31 19:31:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:10</t>
+          <t>2026-08-31 19:31:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:10</t>
+          <t>2026-08-31 19:31:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 17:11:12</t>
+          <t>2026-08-31 19:31:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:07</t>
+          <t>2026-08-31 22:23:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:07</t>
+          <t>2026-08-31 22:23:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:07</t>
+          <t>2026-08-31 22:23:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:07</t>
+          <t>2026-08-31 22:23:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:07</t>
+          <t>2026-08-31 22:23:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:08</t>
+          <t>2026-08-31 22:23:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:08</t>
+          <t>2026-08-31 22:23:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:08</t>
+          <t>2026-08-31 22:23:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:08</t>
+          <t>2026-08-31 22:23:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:08</t>
+          <t>2026-08-31 22:23:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:09</t>
+          <t>2026-08-31 22:23:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:09</t>
+          <t>2026-08-31 22:23:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:09</t>
+          <t>2026-08-31 22:23:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:09</t>
+          <t>2026-08-31 22:23:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:09</t>
+          <t>2026-08-31 22:23:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:10</t>
+          <t>2026-08-31 22:23:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
